--- a/artfynd/A 45450-2025 artfynd.xlsx
+++ b/artfynd/A 45450-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100130</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,8 +885,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000785</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 45450-2025 artfynd.xlsx
+++ b/artfynd/A 45450-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129100130</v>
+        <v>135942397</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Yxtjärnen, Yxtjärnen, Dlr</t>
+          <t>Knivtjärnen, Knivtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483363</v>
+        <v>483107</v>
       </c>
       <c r="R2" t="n">
-        <v>6851268</v>
+        <v>6851030</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,55 +776,51 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129100130</t>
+          <t>https://artportalen.se/Sighting/135942397</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000785</v>
+        <v>129100130</v>
       </c>
       <c r="B3" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Yxtjärnen, Yxtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483325</v>
+        <v>483363</v>
       </c>
       <c r="R3" t="n">
-        <v>6851151</v>
+        <v>6851268</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,16 +867,331 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129100130</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135942911</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mollika, Mollika, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483405</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6851228</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135942911</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135943090</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yxtjärnen, Yxtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483376</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6851250</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135943090</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129000785</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>483325</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6851151</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129000785</t>
         </is>
@@ -895,6 +1201,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
